--- a/backend/tests/fixtures/synthetic_project_evidence/approved_boq.xlsx
+++ b/backend/tests/fixtures/synthetic_project_evidence/approved_boq.xlsx
@@ -1,154 +1,30 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
-  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <workbookPr/>
   <sheets>
-    <sheet sheetId="1" name="BOQ Items" state="visible" r:id="rId4"/>
+    <sheet name="BOQ Items" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="171027"/>
+  <definedNames/>
+  <calcPr calcId="171027" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="40">
-  <si>
-    <t>Item Code</t>
-  </si>
-  <si>
-    <t>Item Number</t>
-  </si>
-  <si>
-    <t>Description</t>
-  </si>
-  <si>
-    <t>Unit</t>
-  </si>
-  <si>
-    <t>Quantity</t>
-  </si>
-  <si>
-    <t>Rate</t>
-  </si>
-  <si>
-    <t>Amount</t>
-  </si>
-  <si>
-    <t>EW-01</t>
-  </si>
-  <si>
-    <t>1.1</t>
-  </si>
-  <si>
-    <t>Earthwork in excavation for foundation</t>
-  </si>
-  <si>
-    <t>CUM</t>
-  </si>
-  <si>
-    <t>CC-01</t>
-  </si>
-  <si>
-    <t>2.1</t>
-  </si>
-  <si>
-    <t>Providing and laying PCC 1:4:8</t>
-  </si>
-  <si>
-    <t>RCC-01</t>
-  </si>
-  <si>
-    <t>3.1</t>
-  </si>
-  <si>
-    <t>RCC work in columns and footings (M25)</t>
-  </si>
-  <si>
-    <t>ST-01</t>
-  </si>
-  <si>
-    <t>4.1</t>
-  </si>
-  <si>
-    <t>Thermo-mechanically treated steel reinforcement</t>
-  </si>
-  <si>
-    <t>MT</t>
-  </si>
-  <si>
-    <t>BW-01</t>
-  </si>
-  <si>
-    <t>5.1</t>
-  </si>
-  <si>
-    <t>Brick work with common burnt clay F.P.S.</t>
-  </si>
-  <si>
-    <t>PL-01</t>
-  </si>
-  <si>
-    <t>6.1</t>
-  </si>
-  <si>
-    <t>12 mm cement plaster of mix 1:6</t>
-  </si>
-  <si>
-    <t>SQM</t>
-  </si>
-  <si>
-    <t>FL-01</t>
-  </si>
-  <si>
-    <t>7.1</t>
-  </si>
-  <si>
-    <t>Vitrified floor tiles 600x600mm</t>
-  </si>
-  <si>
-    <t>PT-01</t>
-  </si>
-  <si>
-    <t>8.1</t>
-  </si>
-  <si>
-    <t>Wall painting with premium acrylic emulsion</t>
-  </si>
-  <si>
-    <t>DR-01</t>
-  </si>
-  <si>
-    <t>9.1</t>
-  </si>
-  <si>
-    <t>Flush door shutters 35mm thick</t>
-  </si>
-  <si>
-    <t>AL-01</t>
-  </si>
-  <si>
-    <t>10.1</t>
-  </si>
-  <si>
-    <t>Aluminum glazed windows</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="1" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
+  <fonts count="1">
     <font>
+      <name val="Calibri"/>
+      <family val="2"/>
       <color theme="1"/>
-      <family val="2"/>
+      <sz val="11"/>
       <scheme val="minor"/>
-      <sz val="11"/>
-      <name val="Calibri"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -167,21 +43,80 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -506,272 +441,370 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:G11"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelRow="0"/>
   <cols>
-    <col min="1" max="2" width="15" customWidth="1"/>
-    <col min="3" max="3" width="40" customWidth="1"/>
-    <col min="4" max="4" width="10" customWidth="1"/>
-    <col min="5" max="6" width="15" customWidth="1"/>
-    <col min="7" max="7" width="20" customWidth="1"/>
+    <col width="15" customWidth="1" min="1" max="2"/>
+    <col width="40" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="6"/>
+    <col width="20" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>7</v>
-      </c>
-      <c r="B2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E2">
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Item Code</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Item Number</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Quantity</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Rate</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Amount</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>EW-01</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>1.1</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Earthwork in excavation for foundation</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>CUM</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
         <v>50000</v>
       </c>
-      <c r="F2">
+      <c r="F2" t="n">
         <v>450</v>
       </c>
-      <c r="G2">
+      <c r="G2" t="n">
         <v>22500000</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>11</v>
-      </c>
-      <c r="B3" t="s">
-        <v>12</v>
-      </c>
-      <c r="C3" t="s">
-        <v>13</v>
-      </c>
-      <c r="D3" t="s">
-        <v>10</v>
-      </c>
-      <c r="E3">
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>CC-01</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>2.1</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Providing and laying PCC 1:4:8</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>CUM</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
         <v>10000</v>
       </c>
-      <c r="F3">
+      <c r="F3" t="n">
         <v>4500</v>
       </c>
-      <c r="G3">
+      <c r="G3" t="n">
         <v>45000000</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B4" t="s">
-        <v>15</v>
-      </c>
-      <c r="C4" t="s">
-        <v>16</v>
-      </c>
-      <c r="D4" t="s">
-        <v>10</v>
-      </c>
-      <c r="E4">
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>RCC-01</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>RCC work in columns and footings (M25)</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>CUM</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
         <v>22000</v>
       </c>
-      <c r="F4">
+      <c r="F4" t="n">
         <v>8500</v>
       </c>
-      <c r="G4">
+      <c r="G4" t="n">
         <v>187000000</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>17</v>
-      </c>
-      <c r="B5" t="s">
-        <v>18</v>
-      </c>
-      <c r="C5" t="s">
-        <v>19</v>
-      </c>
-      <c r="D5" t="s">
-        <v>20</v>
-      </c>
-      <c r="E5">
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>ST-01</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>4.1</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Thermo-mechanically treated steel reinforcement</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>MT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
         <v>2000</v>
       </c>
-      <c r="F5">
+      <c r="F5" t="n">
         <v>65000</v>
       </c>
-      <c r="G5">
+      <c r="G5" t="n">
         <v>130000000</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>21</v>
-      </c>
-      <c r="B6" t="s">
-        <v>22</v>
-      </c>
-      <c r="C6" t="s">
-        <v>23</v>
-      </c>
-      <c r="D6" t="s">
-        <v>10</v>
-      </c>
-      <c r="E6">
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>BW-01</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>5.1</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Brick work with common burnt clay F.P.S.</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>CUM</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
         <v>10000</v>
       </c>
-      <c r="F6">
+      <c r="F6" t="n">
         <v>6200</v>
       </c>
-      <c r="G6">
+      <c r="G6" t="n">
         <v>62000000</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>24</v>
-      </c>
-      <c r="B7" t="s">
-        <v>25</v>
-      </c>
-      <c r="C7" t="s">
-        <v>26</v>
-      </c>
-      <c r="D7" t="s">
-        <v>27</v>
-      </c>
-      <c r="E7">
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>PL-01</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>6.1</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>12 mm cement plaster of mix 1:6</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>SQM</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
         <v>40680</v>
       </c>
-      <c r="F7">
+      <c r="F7" t="n">
         <v>250</v>
       </c>
-      <c r="G7">
+      <c r="G7" t="n">
         <v>10170000</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>28</v>
-      </c>
-      <c r="B8" t="s">
-        <v>29</v>
-      </c>
-      <c r="C8" t="s">
-        <v>30</v>
-      </c>
-      <c r="D8" t="s">
-        <v>27</v>
-      </c>
-      <c r="E8">
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>FL-01</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>7.1</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Vitrified floor tiles 600x600mm</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>SQM</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
         <v>8000</v>
       </c>
-      <c r="F8">
+      <c r="F8" t="n">
         <v>1200</v>
       </c>
-      <c r="G8">
+      <c r="G8" t="n">
         <v>9600000</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>31</v>
-      </c>
-      <c r="B9" t="s">
-        <v>32</v>
-      </c>
-      <c r="C9" t="s">
-        <v>33</v>
-      </c>
-      <c r="D9" t="s">
-        <v>27</v>
-      </c>
-      <c r="E9">
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>PT-01</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>8.1</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Wall painting with premium acrylic emulsion</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>SQM</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
         <v>30000</v>
       </c>
-      <c r="F9">
+      <c r="F9" t="n">
         <v>150</v>
       </c>
-      <c r="G9">
+      <c r="G9" t="n">
         <v>4500000</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>34</v>
-      </c>
-      <c r="B10" t="s">
-        <v>35</v>
-      </c>
-      <c r="C10" t="s">
-        <v>36</v>
-      </c>
-      <c r="D10" t="s">
-        <v>27</v>
-      </c>
-      <c r="E10">
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>DR-01</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>9.1</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Flush door shutters 35mm thick</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>SQM</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
         <v>500</v>
       </c>
-      <c r="F10">
+      <c r="F10" t="n">
         <v>3500</v>
       </c>
-      <c r="G10">
+      <c r="G10" t="n">
         <v>1750000</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>37</v>
-      </c>
-      <c r="B11" t="s">
-        <v>38</v>
-      </c>
-      <c r="C11" t="s">
-        <v>39</v>
-      </c>
-      <c r="D11" t="s">
-        <v>27</v>
-      </c>
-      <c r="E11">
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>AL-01</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>10.1</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Aluminum glazed windows</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>SQM</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
         <v>2600</v>
       </c>
-      <c r="F11">
+      <c r="F11" t="n">
         <v>4800</v>
       </c>
-      <c r="G11">
+      <c r="G11" t="n">
         <v>12480000</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" scale="100" fitToHeight="1" fitToWidth="1" horizontalDpi="4294967295" verticalDpi="4294967295"/>
 </worksheet>
 </file>